--- a/sample/sample_input.xlsx
+++ b/sample/sample_input.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="22">
   <si>
     <t>Wing</t>
   </si>
@@ -50,13 +50,16 @@
     <t>PAIR-1</t>
   </si>
   <si>
-    <t>GROUP-1</t>
+    <t>PREF-3</t>
+  </si>
+  <si>
+    <t>PREF-1</t>
   </si>
   <si>
     <t>PAIR-2</t>
   </si>
   <si>
-    <t>FLOOR-1</t>
+    <t>PREF-2</t>
   </si>
   <si>
     <t>Type</t>
@@ -65,10 +68,7 @@
     <t>pair</t>
   </si>
   <si>
-    <t>same-wing</t>
-  </si>
-  <si>
-    <t>floor-pref</t>
+    <t>pref</t>
   </si>
   <si>
     <t>Randomisation Seed</t>
@@ -2926,6 +2926,7 @@
       <c r="A3" s="1">
         <v>1.0</v>
       </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="1">
@@ -2977,13 +2978,16 @@
       <c r="A12" s="1">
         <v>10.0</v>
       </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1">
         <v>11.0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -3001,7 +3005,7 @@
         <v>14.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -3034,7 +3038,7 @@
         <v>20.0</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -3052,7 +3056,7 @@
         <v>23.0</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -3075,7 +3079,7 @@
         <v>27.0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -3093,7 +3097,7 @@
         <v>30.0</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1"/>
@@ -4083,7 +4087,7 @@
         <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -4097,7 +4101,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -4105,10 +4109,10 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -4116,10 +4120,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -4127,13 +4131,27 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="2">
         <v>5.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2">
+        <v>10.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/sample/sample_input.xlsx
+++ b/sample/sample_input.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="25">
   <si>
     <t>Wing</t>
   </si>
@@ -59,10 +59,19 @@
     <t>PAIR-2</t>
   </si>
   <si>
+    <t>PREF-4</t>
+  </si>
+  <si>
+    <t>PREF-5</t>
+  </si>
+  <si>
     <t>PREF-2</t>
   </si>
   <si>
     <t>Type</t>
+  </si>
+  <si>
+    <t>Unit</t>
   </si>
   <si>
     <t>pair</t>
@@ -351,10 +360,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="2" width="8.78"/>
-    <col customWidth="1" min="3" max="3" width="16.78"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -374,7 +379,7 @@
       <c r="B2" s="1">
         <v>1.0</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -385,7 +390,7 @@
       <c r="B3" s="1">
         <v>2.0</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -396,7 +401,7 @@
       <c r="B4" s="1">
         <v>3.0</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -407,7 +412,7 @@
       <c r="B5" s="1">
         <v>4.0</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -418,7 +423,7 @@
       <c r="B6" s="1">
         <v>5.0</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -429,7 +434,7 @@
       <c r="B7" s="1">
         <v>6.0</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -440,7 +445,7 @@
       <c r="B8" s="1">
         <v>7.0</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -451,7 +456,7 @@
       <c r="B9" s="1">
         <v>8.0</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -462,7 +467,7 @@
       <c r="B10" s="1">
         <v>9.0</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -473,7 +478,7 @@
       <c r="B11" s="1">
         <v>10.0</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -484,7 +489,7 @@
       <c r="B12" s="1">
         <v>11.0</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -495,7 +500,7 @@
       <c r="B13" s="1">
         <v>12.0</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -506,7 +511,7 @@
       <c r="B14" s="1">
         <v>13.0</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -517,7 +522,7 @@
       <c r="B15" s="1">
         <v>14.0</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -528,7 +533,7 @@
       <c r="B16" s="1">
         <v>15.0</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -539,7 +544,7 @@
       <c r="B17" s="1">
         <v>16.0</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -550,7 +555,7 @@
       <c r="B18" s="1">
         <v>17.0</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -561,7 +566,7 @@
       <c r="B19" s="1">
         <v>18.0</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -572,7 +577,7 @@
       <c r="B20" s="1">
         <v>19.0</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -583,7 +588,7 @@
       <c r="B21" s="1">
         <v>20.0</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -594,7 +599,7 @@
       <c r="B22" s="1">
         <v>21.0</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -605,7 +610,7 @@
       <c r="B23" s="1">
         <v>22.0</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -616,7 +621,7 @@
       <c r="B24" s="1">
         <v>23.0</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -627,7 +632,7 @@
       <c r="B25" s="1">
         <v>24.0</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -638,7 +643,7 @@
       <c r="B26" s="1">
         <v>25.0</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -649,7 +654,7 @@
       <c r="B27" s="1">
         <v>26.0</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -660,7 +665,7 @@
       <c r="B28" s="1">
         <v>27.0</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -671,7 +676,7 @@
       <c r="B29" s="1">
         <v>28.0</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -682,7 +687,7 @@
       <c r="B30" s="1">
         <v>29.0</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -693,7 +698,7 @@
       <c r="B31" s="1">
         <v>30.0</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -1674,10 +1679,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="2" width="8.78"/>
-    <col customWidth="1" min="3" max="3" width="16.78"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -2926,7 +2927,6 @@
       <c r="A3" s="1">
         <v>1.0</v>
       </c>
-      <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="1">
@@ -2968,6 +2968,9 @@
       <c r="A10" s="1">
         <v>8.0</v>
       </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1">
@@ -2978,15 +2981,15 @@
       <c r="A12" s="1">
         <v>10.0</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>11</v>
+      <c r="D12" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1">
         <v>11.0</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3022,11 +3025,17 @@
       <c r="A19" s="1">
         <v>17.0</v>
       </c>
+      <c r="D19" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1">
         <v>18.0</v>
       </c>
+      <c r="D20" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1">
@@ -3037,7 +3046,7 @@
       <c r="A22" s="1">
         <v>20.0</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3078,7 +3087,7 @@
       <c r="A29" s="1">
         <v>27.0</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3096,8 +3105,8 @@
       <c r="A32" s="1">
         <v>30.0</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>14</v>
+      <c r="D32" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1"/>
@@ -4079,7 +4088,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="16.78"/>
     <col customWidth="1" min="2" max="2" width="12.78"/>
-    <col customWidth="1" min="3" max="4" width="8.78"/>
+    <col customWidth="1" min="3" max="5" width="8.78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4087,13 +4096,16 @@
         <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2">
@@ -4101,7 +4113,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -4112,46 +4124,71 @@
         <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2">
-        <v>10.0</v>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -5134,6 +5171,23 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1">
+      <c r="A1001" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1001" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1001" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1001" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E1001" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -5142,29 +5196,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="50.78"/>
-    <col customWidth="1" min="2" max="2" width="20.78"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/sample/sample_input.xlsx
+++ b/sample/sample_input.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="25">
   <si>
     <t>Wing</t>
   </si>
@@ -5171,23 +5171,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1">
-      <c r="A1001" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1001" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1001" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1001" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="E1001" s="1">
-        <v>1.0</v>
-      </c>
-    </row>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
